--- a/backend/outputs/output_basicat/LOG/prod/sgic.xlsx
+++ b/backend/outputs/output_basicat/LOG/prod/sgic.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -503,34 +503,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-149</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-167</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-179</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SGIC-LOGIS-PROD-191</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
